--- a/Vulnerability Test Results/endpoint-inventory.xlsx
+++ b/Vulnerability Test Results/endpoint-inventory.xlsx
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total Endpoints Discovered: 47 | Generated: 2026-10-28 11:47 UTC</t>
+          <t>Total Endpoints Discovered: 47 | Generated: 2026-10-29 07:03 UTC</t>
         </is>
       </c>
     </row>
